--- a/data/trans_orig/IP16B98-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16B98-Habitat-trans_orig.xlsx
@@ -1074,64 +1074,64 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>4070</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6538</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>91,1%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>62,24%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>4102</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6538</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>91,1%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>62,73%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4775</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>85,9%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>42,2%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4102</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2682</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4775</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>85,9%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>56,17%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>15</t>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7588</t>
+          <t>7456</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2436</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2093</t>
+          <t>2760</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3725</t>
+          <t>3857</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2525</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>48,57%</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4633</t>
+          <t>4620</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>5313</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>43,39%</t>
         </is>
       </c>
     </row>
@@ -2103,7 +2103,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12494</t>
+          <t>13030</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2118,7 +2118,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>77,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17006</t>
+          <t>17007</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32418</t>
+          <t>32484</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38513</t>
+          <t>38602</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5797</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>7118</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5430</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15643</t>
+          <t>15335</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,31%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3234</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2188</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3862</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>2916</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>3215</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>45,96%</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>5719</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -3792,7 +3792,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2536</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>61,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2436</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>33,52%</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19164</t>
+          <t>18807</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18540</t>
+          <t>18582</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>38830</t>
+          <t>38766</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44216</t>
+          <t>44211</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>555</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
